--- a/EKG_Kalite_Yönetim_Sistemi/16_Ürün Tasarımı ve Teknik Doğrulama/02_DFMEA ve Tasarım Gözden Geçirme/EKG-TAS-LST-01_dfmea_risk_azaltma_ve_kapanis_takip_listesi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/16_Ürün Tasarımı ve Teknik Doğrulama/02_DFMEA ve Tasarım Gözden Geçirme/EKG-TAS-LST-01_dfmea_risk_azaltma_ve_kapanis_takip_listesi.xlsx
@@ -925,7 +925,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-TAS-LST-01&amp;C&amp;"Arial,Regular"&amp;11DFMEA Risk Azaltma ve Kapanış Takip Listesi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 28.09.2026
+Revizyon nedeni: DFMEA risk ve kapanış takibi sadeleştirildi; RPN oranına bağlı kabul kaldırıldı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>